--- a/data/trans_orig/IP31KM09_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM09_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>57575</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53508</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>59614</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>95,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>68865</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>65831</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>70525</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>92,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>71415</t>
+          <t>52787</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66509</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73474</t>
+          <t>54145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>140280</t>
+          <t>110363</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134278</t>
+          <t>105363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143177</t>
+          <t>112880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2688</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6755</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2535</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>875</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5569</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>777</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>103517</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>95451</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>108220</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>90,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>83,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>94,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>113720</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>106112</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>120725</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>90,51%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>84,45%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>113634</t>
+          <t>87410</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104776</t>
+          <t>80782</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118954</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>227353</t>
+          <t>190927</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>217785</t>
+          <t>180637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>237517</t>
+          <t>197822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11434</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6731</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19500</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9,95%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11929</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4924</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19537</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21647</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>24718</t>
+          <t>23357</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34286</t>
+          <t>33647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54562</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50656</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>56628</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>88,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>52484</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48478</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54386</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61233</t>
+          <t>50932</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55016</t>
+          <t>47206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63421</t>
+          <t>53047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>113717</t>
+          <t>105493</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107734</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117288</t>
+          <t>108652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6643</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3068</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1166</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7074</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58234</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36726</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>67553</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>52,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>63622</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>58319</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>66816</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>91,3%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>95,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61215</t>
+          <t>64859</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36253</t>
+          <t>59248</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72663</t>
+          <t>67650</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>124836</t>
+          <t>123094</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86504</t>
+          <t>97100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136883</t>
+          <t>133144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11582</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2263</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33090</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6060</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2866</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11363</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39114</t>
+          <t>11214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58545</t>
+          <t>43178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37278</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34175</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>38977</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>94,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>32342</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29499</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33732</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>94,57%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>86,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38369</t>
+          <t>33496</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34502</t>
+          <t>30667</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40095</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>70711</t>
+          <t>70775</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66917</t>
+          <t>66919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72904</t>
+          <t>73008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>41217</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>36857</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>44092</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>78,07%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>38043</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>33931</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>40826</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>85,89%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>76,61%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47667</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43479</t>
+          <t>33871</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50912</t>
+          <t>41092</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>85709</t>
+          <t>79441</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79706</t>
+          <t>73551</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90558</t>
+          <t>84049</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18366</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,107 +2778,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>127765</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>120630</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>132860</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>90,89%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>111484</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>104552</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>116327</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>90,13%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>84,52%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>142130</t>
+          <t>109144</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>134416</t>
+          <t>102179</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147104</t>
+          <t>114531</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>236910</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>227495</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>245063</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>90,29%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>86,7%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>253613</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>244659</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>261429</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>90,99%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>87,77%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19144</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,67 +2931,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>25484</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>17331</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>34899</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>6,61%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>13,3%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>25127</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>17311</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>34081</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>156709</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>155074</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>126819</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>123529</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>128155</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>96,01%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>153648</t>
+          <t>136295</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>151571</t>
+          <t>133285</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,27 +3196,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>280466</t>
+          <t>293003</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>276928</t>
+          <t>289983</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282308</t>
+          <t>294505</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5136</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>435</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,22 +3309,22 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>531</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>636857</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>607353</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>650829</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>88,43%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>844</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>607377</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>594531</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>618007</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>92,99%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>689310</t>
+          <t>573148</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>643635</t>
+          <t>561227</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>704732</t>
+          <t>582761</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1296687</t>
+          <t>1210004</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1256992</t>
+          <t>1181271</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1314187</t>
+          <t>1226927</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>35995</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>79471</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>45757</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>35127</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>58603</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>55423</t>
+          <t>45060</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40001</t>
+          <t>35447</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>101098</t>
+          <t>56981</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>101180</t>
+          <t>95027</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>83680</t>
+          <t>78104</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>140875</t>
+          <t>123760</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
